--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/154.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/154.xlsx
@@ -426,13 +426,13 @@
         <v>-5.114272881996766</v>
       </c>
       <c r="E2">
-        <v>-5.682702596400995</v>
+        <v>-4.672812136424437</v>
       </c>
       <c r="F2">
-        <v>-1.93855487529397</v>
+        <v>-2.283860570125683</v>
       </c>
       <c r="G2">
-        <v>-5.63070942568234</v>
+        <v>-5.366623897469138</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.898102271770616</v>
       </c>
       <c r="E3">
-        <v>-6.547944539624548</v>
+        <v>-5.620268525257244</v>
       </c>
       <c r="F3">
-        <v>-1.908626792756953</v>
+        <v>-2.27118300427259</v>
       </c>
       <c r="G3">
-        <v>-5.696625697914769</v>
+        <v>-4.380617635143686</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.672581734857646</v>
       </c>
       <c r="E4">
-        <v>-6.015536379016751</v>
+        <v>-6.004409918379905</v>
       </c>
       <c r="F4">
-        <v>-2.147994439640133</v>
+        <v>-2.104395807641043</v>
       </c>
       <c r="G4">
-        <v>-4.902412580861453</v>
+        <v>-4.143039645063428</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.437274624081915</v>
       </c>
       <c r="E5">
-        <v>-7.8068557852829</v>
+        <v>-7.433107240007842</v>
       </c>
       <c r="F5">
-        <v>-2.041640668888797</v>
+        <v>-2.069564571589825</v>
       </c>
       <c r="G5">
-        <v>-4.456098073439069</v>
+        <v>-3.850963454315689</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.163451374472688</v>
       </c>
       <c r="E6">
-        <v>-8.339562825175202</v>
+        <v>-7.133462643394302</v>
       </c>
       <c r="F6">
-        <v>-1.848615424503206</v>
+        <v>-2.345315486321353</v>
       </c>
       <c r="G6">
-        <v>-4.664198966037656</v>
+        <v>-3.906597172103141</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.82819951260318</v>
       </c>
       <c r="E7">
-        <v>-8.162703272805636</v>
+        <v>-8.139454087250256</v>
       </c>
       <c r="F7">
-        <v>-1.65123736440903</v>
+        <v>-2.080089881103836</v>
       </c>
       <c r="G7">
-        <v>-4.068724518797869</v>
+        <v>-2.937564076757533</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.415930874827041</v>
       </c>
       <c r="E8">
-        <v>-9.45448218281166</v>
+        <v>-8.291905164718479</v>
       </c>
       <c r="F8">
-        <v>-1.834659807976354</v>
+        <v>-2.16023648636648</v>
       </c>
       <c r="G8">
-        <v>-3.784616811163155</v>
+        <v>-2.651201887610575</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.917236222297372</v>
       </c>
       <c r="E9">
-        <v>-10.33767952547562</v>
+        <v>-9.10324468182873</v>
       </c>
       <c r="F9">
-        <v>-1.942605995025664</v>
+        <v>-1.85517038328721</v>
       </c>
       <c r="G9">
-        <v>-2.642663990664794</v>
+        <v>-2.408912991227935</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.340753444889107</v>
       </c>
       <c r="E10">
-        <v>-10.66947175906962</v>
+        <v>-10.05522954466921</v>
       </c>
       <c r="F10">
-        <v>-1.625878273438056</v>
+        <v>-2.222449205842688</v>
       </c>
       <c r="G10">
-        <v>-2.668962964428765</v>
+        <v>-1.639144942436598</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.700415925896692</v>
       </c>
       <c r="E11">
-        <v>-11.56269514318656</v>
+        <v>-10.32718705119985</v>
       </c>
       <c r="F11">
-        <v>-1.691556933310203</v>
+        <v>-2.087547552259641</v>
       </c>
       <c r="G11">
-        <v>-2.374450212164122</v>
+        <v>-2.009105027541232</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.029563791667354</v>
       </c>
       <c r="E12">
-        <v>-10.98352143150156</v>
+        <v>-11.06739782707163</v>
       </c>
       <c r="F12">
-        <v>-1.755373155025793</v>
+        <v>-1.746857568318475</v>
       </c>
       <c r="G12">
-        <v>-1.565564757280757</v>
+        <v>-1.250827882316706</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.3609529794731628</v>
       </c>
       <c r="E13">
-        <v>-12.14207716467592</v>
+        <v>-12.61643028850539</v>
       </c>
       <c r="F13">
-        <v>-1.281061943734214</v>
+        <v>-1.598525296719544</v>
       </c>
       <c r="G13">
-        <v>-0.4931863618357197</v>
+        <v>-0.5805946957090968</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.2606611730572133</v>
       </c>
       <c r="E14">
-        <v>-13.34700900016285</v>
+        <v>-13.2440179158064</v>
       </c>
       <c r="F14">
-        <v>-1.138697867877616</v>
+        <v>-1.630760046922398</v>
       </c>
       <c r="G14">
-        <v>-0.02005974609077804</v>
+        <v>0.1453649039610639</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.7982463315097299</v>
       </c>
       <c r="E15">
-        <v>-13.68254628176118</v>
+        <v>-13.35141973384632</v>
       </c>
       <c r="F15">
-        <v>-1.206289644495613</v>
+        <v>-1.059852277024505</v>
       </c>
       <c r="G15">
-        <v>0.6719369668919997</v>
+        <v>0.2795346935766466</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.215854375899403</v>
       </c>
       <c r="E16">
-        <v>-15.21759934393326</v>
+        <v>-15.01212436430923</v>
       </c>
       <c r="F16">
-        <v>-0.8307612978266117</v>
+        <v>-0.8321312034434668</v>
       </c>
       <c r="G16">
-        <v>0.7992737905145266</v>
+        <v>1.720562198092766</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.488093585559551</v>
       </c>
       <c r="E17">
-        <v>-15.47247544650697</v>
+        <v>-15.44995081679282</v>
       </c>
       <c r="F17">
-        <v>-0.518538427715471</v>
+        <v>-1.155596801848312</v>
       </c>
       <c r="G17">
-        <v>1.490942759488916</v>
+        <v>1.502307862325234</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.598667994636409</v>
       </c>
       <c r="E18">
-        <v>-17.19725345570441</v>
+        <v>-16.51197759801969</v>
       </c>
       <c r="F18">
-        <v>-0.5770341894081424</v>
+        <v>-0.4504818334112916</v>
       </c>
       <c r="G18">
-        <v>1.56328480061307</v>
+        <v>1.964678515613084</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.540223739320376</v>
       </c>
       <c r="E19">
-        <v>-17.00600241293847</v>
+        <v>-17.72483426302003</v>
       </c>
       <c r="F19">
-        <v>-0.3097244272059066</v>
+        <v>-0.2826897753763976</v>
       </c>
       <c r="G19">
-        <v>2.34375584313287</v>
+        <v>2.392854544025802</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.318211217561536</v>
       </c>
       <c r="E20">
-        <v>-19.51642990620065</v>
+        <v>-18.18606386917527</v>
       </c>
       <c r="F20">
-        <v>0.03641746434915844</v>
+        <v>0.3416078883427903</v>
       </c>
       <c r="G20">
-        <v>1.916142607461829</v>
+        <v>2.448842490185956</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.9436472584904799</v>
       </c>
       <c r="E21">
-        <v>-19.0682377767135</v>
+        <v>-19.16348064204282</v>
       </c>
       <c r="F21">
-        <v>0.4529463734629721</v>
+        <v>0.3762443285664088</v>
       </c>
       <c r="G21">
-        <v>1.942789188507423</v>
+        <v>2.053646116435458</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.4385732775163426</v>
       </c>
       <c r="E22">
-        <v>-19.62762658545899</v>
+        <v>-19.70023160922397</v>
       </c>
       <c r="F22">
-        <v>0.4307079749983713</v>
+        <v>0.4304078627273956</v>
       </c>
       <c r="G22">
-        <v>1.725935213503003</v>
+        <v>2.897914682042553</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.1735023773826769</v>
       </c>
       <c r="E23">
-        <v>-19.75891157541536</v>
+        <v>-20.39023972224672</v>
       </c>
       <c r="F23">
-        <v>0.6325275383323973</v>
+        <v>0.6748710833935019</v>
       </c>
       <c r="G23">
-        <v>2.205643193780016</v>
+        <v>2.05304359714731</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.862925589274281</v>
       </c>
       <c r="E24">
-        <v>-20.28591726653201</v>
+        <v>-20.47036201286442</v>
       </c>
       <c r="F24">
-        <v>1.062624056023781</v>
+        <v>0.9687324671210377</v>
       </c>
       <c r="G24">
-        <v>1.674085449266938</v>
+        <v>2.317443627186743</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.5993469493196</v>
       </c>
       <c r="E25">
-        <v>-20.42796191073061</v>
+        <v>-21.38677571237465</v>
       </c>
       <c r="F25">
-        <v>1.333208130206188</v>
+        <v>1.051338567670359</v>
       </c>
       <c r="G25">
-        <v>1.905313813002873</v>
+        <v>2.189848581012153</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.35145213642252</v>
       </c>
       <c r="E26">
-        <v>-19.98600096147801</v>
+        <v>-21.13809909071744</v>
       </c>
       <c r="F26">
-        <v>1.181221457207379</v>
+        <v>0.8946894644564971</v>
       </c>
       <c r="G26">
-        <v>1.099662761111376</v>
+        <v>1.817011631833893</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.088207817010356</v>
       </c>
       <c r="E27">
-        <v>-21.37885088286123</v>
+        <v>-20.58131415452636</v>
       </c>
       <c r="F27">
-        <v>1.187483430397027</v>
+        <v>1.124949218619985</v>
       </c>
       <c r="G27">
-        <v>1.05135859114787</v>
+        <v>1.707406090119702</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.783637536609815</v>
       </c>
       <c r="E28">
-        <v>-20.80457245157851</v>
+        <v>-21.10310757206017</v>
       </c>
       <c r="F28">
-        <v>1.162383275343227</v>
+        <v>1.077103879208644</v>
       </c>
       <c r="G28">
-        <v>1.097001082497802</v>
+        <v>1.643840305220156</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.409684751450048</v>
       </c>
       <c r="E29">
-        <v>-21.39623569457667</v>
+        <v>-20.41016500788046</v>
       </c>
       <c r="F29">
-        <v>1.082987346684501</v>
+        <v>0.8666166933994175</v>
       </c>
       <c r="G29">
-        <v>0.3499069601049342</v>
+        <v>2.037563486205678</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.945625210645035</v>
       </c>
       <c r="E30">
-        <v>-20.75358636272615</v>
+        <v>-20.53031448025197</v>
       </c>
       <c r="F30">
-        <v>0.9890688347811956</v>
+        <v>0.9697270344359336</v>
       </c>
       <c r="G30">
-        <v>0.1958308601617139</v>
+        <v>1.256724973131019</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.368403787844334</v>
       </c>
       <c r="E31">
-        <v>-19.68966215089007</v>
+        <v>-20.19603158595376</v>
       </c>
       <c r="F31">
-        <v>1.198214621680044</v>
+        <v>1.349065777537483</v>
       </c>
       <c r="G31">
-        <v>0.7397998399015198</v>
+        <v>0.3230849201457591</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.667817095482771</v>
       </c>
       <c r="E32">
-        <v>-19.95107736993086</v>
+        <v>-20.03514396140925</v>
       </c>
       <c r="F32">
-        <v>0.845773539846319</v>
+        <v>0.6106692292875021</v>
       </c>
       <c r="G32">
-        <v>-0.1754733064318639</v>
+        <v>1.32108859950553</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.835271982805216</v>
       </c>
       <c r="E33">
-        <v>-19.52975720520522</v>
+        <v>-20.17506475129825</v>
       </c>
       <c r="F33">
-        <v>0.848152266131309</v>
+        <v>0.6420962894734825</v>
       </c>
       <c r="G33">
-        <v>-0.3361605658170088</v>
+        <v>0.9660822486017839</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.876878131986857</v>
       </c>
       <c r="E34">
-        <v>-19.41310824324164</v>
+        <v>-19.69328493009621</v>
       </c>
       <c r="F34">
-        <v>0.7400389981079196</v>
+        <v>0.5978903062558212</v>
       </c>
       <c r="G34">
-        <v>-0.1165753907426902</v>
+        <v>0.956683609815793</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.800199017584767</v>
       </c>
       <c r="E35">
-        <v>-18.80981587899178</v>
+        <v>-18.56271516628924</v>
       </c>
       <c r="F35">
-        <v>0.7769140066430118</v>
+        <v>0.6079341691715382</v>
       </c>
       <c r="G35">
-        <v>-0.06915513643816974</v>
+        <v>0.8362227892783323</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.62413870908641</v>
       </c>
       <c r="E36">
-        <v>-18.42474614869755</v>
+        <v>-18.52616132409933</v>
       </c>
       <c r="F36">
-        <v>0.8200905810156374</v>
+        <v>0.467666128094024</v>
       </c>
       <c r="G36">
-        <v>-0.1735300162003117</v>
+        <v>1.271794576425782</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.369583821231552</v>
       </c>
       <c r="E37">
-        <v>-16.64119760382856</v>
+        <v>-17.50298884985827</v>
       </c>
       <c r="F37">
-        <v>0.6384379288088173</v>
+        <v>0.339275089529348</v>
       </c>
       <c r="G37">
-        <v>0.6081957230788723</v>
+        <v>1.305966027482139</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.06456129088307</v>
       </c>
       <c r="E38">
-        <v>-17.19133474017639</v>
+        <v>-17.42293901482468</v>
       </c>
       <c r="F38">
-        <v>0.5663840607740688</v>
+        <v>0.7305795226749998</v>
       </c>
       <c r="G38">
-        <v>0.5435374581513667</v>
+        <v>1.212211377809979</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.735331294403518</v>
       </c>
       <c r="E39">
-        <v>-16.90633975697766</v>
+        <v>-16.09902605326023</v>
       </c>
       <c r="F39">
-        <v>0.796667570526288</v>
+        <v>0.3627226474603867</v>
       </c>
       <c r="G39">
-        <v>1.184829855654667</v>
+        <v>2.106538702516394</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.410126903718575</v>
       </c>
       <c r="E40">
-        <v>-16.6967755653247</v>
+        <v>-16.37716945528535</v>
       </c>
       <c r="F40">
-        <v>0.7857764249458109</v>
+        <v>0.7069379607693198</v>
       </c>
       <c r="G40">
-        <v>0.9492150190791971</v>
+        <v>1.454420821099677</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.110915934777314</v>
       </c>
       <c r="E41">
-        <v>-15.82702326198951</v>
+        <v>-15.17340596609241</v>
       </c>
       <c r="F41">
-        <v>0.724979538558006</v>
+        <v>0.2700037927880266</v>
       </c>
       <c r="G41">
-        <v>1.291578396568466</v>
+        <v>2.44582327265414</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.859233651427462</v>
       </c>
       <c r="E42">
-        <v>-15.24580720852704</v>
+        <v>-15.1374453539975</v>
       </c>
       <c r="F42">
-        <v>0.609912217859922</v>
+        <v>0.3890319619806246</v>
       </c>
       <c r="G42">
-        <v>1.280829055202453</v>
+        <v>1.840539678981493</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.667445357585708</v>
       </c>
       <c r="E43">
-        <v>-15.07507015301585</v>
+        <v>-13.71015638778595</v>
       </c>
       <c r="F43">
-        <v>0.746307306121229</v>
+        <v>0.1302346190738759</v>
       </c>
       <c r="G43">
-        <v>0.9032679575396524</v>
+        <v>2.338849614643671</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.546872491862402</v>
       </c>
       <c r="E44">
-        <v>-13.72450259344225</v>
+        <v>-13.53636261231957</v>
       </c>
       <c r="F44">
-        <v>0.7135626026136029</v>
+        <v>0.2484780619853736</v>
       </c>
       <c r="G44">
-        <v>1.26857672616161</v>
+        <v>2.314629663478363</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.497539617589616</v>
       </c>
       <c r="E45">
-        <v>-13.14133929615648</v>
+        <v>-13.05339633092752</v>
       </c>
       <c r="F45">
-        <v>0.3471849087240103</v>
+        <v>0.2305679317876689</v>
       </c>
       <c r="G45">
-        <v>1.510690163630669</v>
+        <v>1.665915022876016</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.518629030985106</v>
       </c>
       <c r="E46">
-        <v>-12.96589715615132</v>
+        <v>-11.51563524129885</v>
       </c>
       <c r="F46">
-        <v>0.7687864278849765</v>
+        <v>0.3210688063254561</v>
       </c>
       <c r="G46">
-        <v>1.402147307034585</v>
+        <v>2.442727912574922</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.599698460799762</v>
       </c>
       <c r="E47">
-        <v>-12.59014249689086</v>
+        <v>-12.17543843269043</v>
       </c>
       <c r="F47">
-        <v>0.5236422136752313</v>
+        <v>0.2547851707936112</v>
       </c>
       <c r="G47">
-        <v>1.11845010704674</v>
+        <v>2.85799943447556</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.731148656773644</v>
       </c>
       <c r="E48">
-        <v>-11.85037098299783</v>
+        <v>-11.00274933213812</v>
       </c>
       <c r="F48">
-        <v>0.4037240017581563</v>
+        <v>0.6213497419812257</v>
       </c>
       <c r="G48">
-        <v>1.37464329469432</v>
+        <v>2.660677678152841</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.896537091366267</v>
       </c>
       <c r="E49">
-        <v>-11.41502160579643</v>
+        <v>-11.02755631275214</v>
       </c>
       <c r="F49">
-        <v>0.3197408689153601</v>
+        <v>-0.07902836206271552</v>
       </c>
       <c r="G49">
-        <v>1.573411759417701</v>
+        <v>2.247306409391744</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.081664122807422</v>
       </c>
       <c r="E50">
-        <v>-10.89196927248848</v>
+        <v>-9.523785949025047</v>
       </c>
       <c r="F50">
-        <v>0.1410544978881582</v>
+        <v>0.2810176755769502</v>
       </c>
       <c r="G50">
-        <v>1.132208734307951</v>
+        <v>1.948099303552414</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.271371041954223</v>
       </c>
       <c r="E51">
-        <v>-10.45936415053573</v>
+        <v>-10.9711496405126</v>
       </c>
       <c r="F51">
-        <v>0.3837265471639024</v>
+        <v>0.05950552103739243</v>
       </c>
       <c r="G51">
-        <v>1.14007127996372</v>
+        <v>1.732188834026686</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.453249560772222</v>
       </c>
       <c r="E52">
-        <v>-10.11688924675765</v>
+        <v>-10.51380093658194</v>
       </c>
       <c r="F52">
-        <v>0.2296375045623482</v>
+        <v>0.2784995831714015</v>
       </c>
       <c r="G52">
-        <v>1.214681044782275</v>
+        <v>1.911842208806316</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.618176259008646</v>
       </c>
       <c r="E53">
-        <v>-9.352573403743046</v>
+        <v>-9.547103061690541</v>
       </c>
       <c r="F53">
-        <v>0.1298846200665638</v>
+        <v>0.1979736803420096</v>
       </c>
       <c r="G53">
-        <v>0.841175365405082</v>
+        <v>1.602273095429067</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.758908094469907</v>
       </c>
       <c r="E54">
-        <v>-9.080851377860801</v>
+        <v>-8.057787586995929</v>
       </c>
       <c r="F54">
-        <v>0.1373945535175776</v>
+        <v>0.1295567929420678</v>
       </c>
       <c r="G54">
-        <v>0.7655327103782746</v>
+        <v>1.234822403843201</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.874047485476374</v>
       </c>
       <c r="E55">
-        <v>-8.528735298371624</v>
+        <v>-7.934264401488705</v>
       </c>
       <c r="F55">
-        <v>0.3044691927727776</v>
+        <v>-0.05699505351416421</v>
       </c>
       <c r="G55">
-        <v>0.9619804826786269</v>
+        <v>0.8211896019845019</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.961946516925929</v>
       </c>
       <c r="E56">
-        <v>-7.718120337102599</v>
+        <v>-7.862678284375452</v>
       </c>
       <c r="F56">
-        <v>0.2762214222120419</v>
+        <v>0.2791433596260277</v>
       </c>
       <c r="G56">
-        <v>0.342104004268872</v>
+        <v>2.027343832125948</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.027212325076192</v>
       </c>
       <c r="E57">
-        <v>-8.712795124413384</v>
+        <v>-7.721797457996827</v>
       </c>
       <c r="F57">
-        <v>0.04734028404794431</v>
+        <v>0.1557172391062543</v>
       </c>
       <c r="G57">
-        <v>0.2616080894814931</v>
+        <v>0.9588718804172512</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.071895959288327</v>
       </c>
       <c r="E58">
-        <v>-8.400076823339701</v>
+        <v>-6.322734470275085</v>
       </c>
       <c r="F58">
-        <v>0.04944502920956333</v>
+        <v>0.2466488816530411</v>
       </c>
       <c r="G58">
-        <v>0.5189765207955137</v>
+        <v>0.5700714806486252</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.103080710482883</v>
       </c>
       <c r="E59">
-        <v>-8.381944813412989</v>
+        <v>-6.886008709719163</v>
       </c>
       <c r="F59">
-        <v>0.2125089332339129</v>
+        <v>-0.2123162193179303</v>
       </c>
       <c r="G59">
-        <v>0.4931012968605701</v>
+        <v>0.4888141403872139</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.123995001120703</v>
       </c>
       <c r="E60">
-        <v>-7.682340863967995</v>
+        <v>-6.953645997497727</v>
       </c>
       <c r="F60">
-        <v>0.1989619128332439</v>
+        <v>-0.06947861539261566</v>
       </c>
       <c r="G60">
-        <v>0.09226044296561479</v>
+        <v>0.7319968840654575</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.140791505029348</v>
       </c>
       <c r="E61">
-        <v>-7.101215379985681</v>
+        <v>-6.013453280973223</v>
       </c>
       <c r="F61">
-        <v>-0.06682749169017002</v>
+        <v>0.09443177944353628</v>
       </c>
       <c r="G61">
-        <v>-0.02083441374696749</v>
+        <v>0.7715843876240623</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.153133370793182</v>
       </c>
       <c r="E62">
-        <v>-6.540431801245822</v>
+        <v>-6.505105175511986</v>
       </c>
       <c r="F62">
-        <v>0.1096939533506262</v>
+        <v>-0.3956048397353993</v>
       </c>
       <c r="G62">
-        <v>-0.5397326321178726</v>
+        <v>0.3230054670528165</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.162310913271549</v>
       </c>
       <c r="E63">
-        <v>-7.034492843956667</v>
+        <v>-6.256967442261689</v>
       </c>
       <c r="F63">
-        <v>-0.07098155230636768</v>
+        <v>-0.3603365008515205</v>
       </c>
       <c r="G63">
-        <v>-0.3921319592494668</v>
+        <v>-0.4991354121697901</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.163205003124245</v>
       </c>
       <c r="E64">
-        <v>-6.858702011452911</v>
+        <v>-5.723726042436481</v>
       </c>
       <c r="F64">
-        <v>-0.1508985202112731</v>
+        <v>-0.5773018357078517</v>
       </c>
       <c r="G64">
-        <v>-0.5420102874488912</v>
+        <v>-0.0152263496034421</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.152439613859261</v>
       </c>
       <c r="E65">
-        <v>-7.287557556927308</v>
+        <v>-5.716942388372991</v>
       </c>
       <c r="F65">
-        <v>-0.1388623552539333</v>
+        <v>-0.2872674773249753</v>
       </c>
       <c r="G65">
-        <v>0.1049166585622485</v>
+        <v>-0.2929248410741271</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.120162334802536</v>
       </c>
       <c r="E66">
-        <v>-6.454046631075503</v>
+        <v>-5.399478246539268</v>
       </c>
       <c r="F66">
-        <v>-0.3514843766371717</v>
+        <v>-0.5289085340497685</v>
       </c>
       <c r="G66">
-        <v>-0.7567355816715596</v>
+        <v>-0.3371173134778582</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.06001936417033</v>
       </c>
       <c r="E67">
-        <v>-6.678328363253392</v>
+        <v>-5.379738628339833</v>
       </c>
       <c r="F67">
-        <v>-0.4295816664452372</v>
+        <v>-0.4355474866286976</v>
       </c>
       <c r="G67">
-        <v>-0.9030815577805817</v>
+        <v>-0.9212399000634842</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.962848742866314</v>
       </c>
       <c r="E68">
-        <v>-6.165868130649384</v>
+        <v>-5.167683775982653</v>
       </c>
       <c r="F68">
-        <v>-0.631577021135877</v>
+        <v>-0.4579585090380812</v>
       </c>
       <c r="G68">
-        <v>-0.9289170551690541</v>
+        <v>-0.117793671501142</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.826918009182023</v>
       </c>
       <c r="E69">
-        <v>-6.542831892469888</v>
+        <v>-5.240805045784507</v>
       </c>
       <c r="F69">
-        <v>-0.4218753534607089</v>
+        <v>-0.8163511577020282</v>
       </c>
       <c r="G69">
-        <v>-1.148863079707153</v>
+        <v>-0.8256114816160967</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.649124585263449</v>
       </c>
       <c r="E70">
-        <v>-7.008798282437144</v>
+        <v>-5.188310975087592</v>
       </c>
       <c r="F70">
-        <v>-0.8147009361381403</v>
+        <v>-0.8695763461081171</v>
       </c>
       <c r="G70">
-        <v>-1.157596298839751</v>
+        <v>-0.3680841564522008</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.435090681402368</v>
       </c>
       <c r="E71">
-        <v>-5.932040375263325</v>
+        <v>-4.885971936439488</v>
       </c>
       <c r="F71">
-        <v>-0.8064387423772926</v>
+        <v>-0.6919288861614434</v>
       </c>
       <c r="G71">
-        <v>-0.7225873044339773</v>
+        <v>-1.359817662560592</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.188167595744934</v>
       </c>
       <c r="E72">
-        <v>-7.35452010207873</v>
+        <v>-5.345372039095623</v>
       </c>
       <c r="F72">
-        <v>-0.6976967431054739</v>
+        <v>-0.3312723298913758</v>
       </c>
       <c r="G72">
-        <v>-1.16872635294278</v>
+        <v>-0.9367100793684985</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.91926419509101</v>
       </c>
       <c r="E73">
-        <v>-7.357988913168606</v>
+        <v>-6.09718023690104</v>
       </c>
       <c r="F73">
-        <v>-0.7615533493219079</v>
+        <v>-0.936156926499107</v>
       </c>
       <c r="G73">
-        <v>-0.6425052078390073</v>
+        <v>-0.5617676232272616</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.635172729532656</v>
       </c>
       <c r="E74">
-        <v>-7.679125647422549</v>
+        <v>-5.940975054480459</v>
       </c>
       <c r="F74">
-        <v>-0.7851632371092792</v>
+        <v>-0.9728244695592765</v>
       </c>
       <c r="G74">
-        <v>-0.7766485130902758</v>
+        <v>-0.2549297099199117</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.347953387199794</v>
       </c>
       <c r="E75">
-        <v>-7.301935461901662</v>
+        <v>-6.492783197737115</v>
       </c>
       <c r="F75">
-        <v>-0.6605342919467295</v>
+        <v>-0.8176276246698724</v>
       </c>
       <c r="G75">
-        <v>-0.3805913974995674</v>
+        <v>-0.6011134569614996</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.06404055442376</v>
       </c>
       <c r="E76">
-        <v>-7.821867676618327</v>
+        <v>-6.15837350616669</v>
       </c>
       <c r="F76">
-        <v>-1.029097499999629</v>
+        <v>-1.089102533429714</v>
       </c>
       <c r="G76">
-        <v>-0.421274691631671</v>
+        <v>0.1802282590351288</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.792444265403137</v>
       </c>
       <c r="E77">
-        <v>-7.807607511968173</v>
+        <v>-7.475480171297614</v>
       </c>
       <c r="F77">
-        <v>-1.206270640024628</v>
+        <v>-0.9051131231446629</v>
       </c>
       <c r="G77">
-        <v>-0.2372712600134392</v>
+        <v>-0.09492773346139594</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.538769327258302</v>
       </c>
       <c r="E78">
-        <v>-8.319619425645422</v>
+        <v>-7.343737805466467</v>
       </c>
       <c r="F78">
-        <v>-0.9462158346210205</v>
+        <v>-1.03324680949808</v>
       </c>
       <c r="G78">
-        <v>0.1787716189978495</v>
+        <v>-0.2840757528476552</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.308449924584976</v>
       </c>
       <c r="E79">
-        <v>-9.400502772640229</v>
+        <v>-8.185327528947957</v>
       </c>
       <c r="F79">
-        <v>-1.052265533836592</v>
+        <v>-1.080165680948889</v>
       </c>
       <c r="G79">
-        <v>-0.5183431973886414</v>
+        <v>-0.2716446543476919</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.104953247508232</v>
       </c>
       <c r="E80">
-        <v>-9.705133219136213</v>
+        <v>-8.47849187925652</v>
       </c>
       <c r="F80">
-        <v>-0.9376551122951127</v>
+        <v>-1.014867902349405</v>
       </c>
       <c r="G80">
-        <v>-0.3033464384317528</v>
+        <v>0.09947081115014744</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.930444927461478</v>
       </c>
       <c r="E81">
-        <v>-10.67143258831494</v>
+        <v>-9.318342668719065</v>
       </c>
       <c r="F81">
-        <v>-1.32785332685883</v>
+        <v>-1.581144124297596</v>
       </c>
       <c r="G81">
-        <v>-0.06846654296600134</v>
+        <v>0.9001163181862663</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.787838850555162</v>
       </c>
       <c r="E82">
-        <v>-11.17734917597786</v>
+        <v>-10.43776785799315</v>
       </c>
       <c r="F82">
-        <v>-1.228562092637396</v>
+        <v>-1.398139779091948</v>
       </c>
       <c r="G82">
-        <v>0.3172484283600239</v>
+        <v>0.7863394890925941</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.678117335487412</v>
       </c>
       <c r="E83">
-        <v>-11.83857883668186</v>
+        <v>-11.55567600847468</v>
       </c>
       <c r="F83">
-        <v>-1.551714909123942</v>
+        <v>-1.651290418557197</v>
       </c>
       <c r="G83">
-        <v>0.5276203551985508</v>
+        <v>1.083669515611157</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.604794005075848</v>
       </c>
       <c r="E84">
-        <v>-13.4225484750848</v>
+        <v>-12.68916210954258</v>
       </c>
       <c r="F84">
-        <v>-1.154733682124398</v>
+        <v>-1.180927386112808</v>
       </c>
       <c r="G84">
-        <v>0.05588747912564226</v>
+        <v>1.630141267778652</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.567791035853598</v>
       </c>
       <c r="E85">
-        <v>-14.61641724857098</v>
+        <v>-12.46055568468737</v>
       </c>
       <c r="F85">
-        <v>-1.488533753480443</v>
+        <v>-1.280776084816477</v>
       </c>
       <c r="G85">
-        <v>0.2893239767362715</v>
+        <v>0.5235848001861793</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.568332819693709</v>
       </c>
       <c r="E86">
-        <v>-14.87202243545992</v>
+        <v>-14.5984844915006</v>
       </c>
       <c r="F86">
-        <v>-1.230762652006899</v>
+        <v>-1.580783039348876</v>
       </c>
       <c r="G86">
-        <v>0.1682639474562027</v>
+        <v>1.36514865008769</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.603495103683484</v>
       </c>
       <c r="E87">
-        <v>-16.8270144777853</v>
+        <v>-15.91574965322179</v>
       </c>
       <c r="F87">
-        <v>-1.836176998243345</v>
+        <v>-1.510465704850406</v>
       </c>
       <c r="G87">
-        <v>0.6042925898880714</v>
+        <v>1.647611016589386</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.67173363774955</v>
       </c>
       <c r="E88">
-        <v>-18.06707368614972</v>
+        <v>-16.70134026712443</v>
       </c>
       <c r="F88">
-        <v>-1.635312409576329</v>
+        <v>-1.510364347671818</v>
       </c>
       <c r="G88">
-        <v>0.9273720396110859</v>
+        <v>0.9072538543689349</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.76922387906911</v>
       </c>
       <c r="E89">
-        <v>-20.12210424777854</v>
+        <v>-19.85729720170601</v>
       </c>
       <c r="F89">
-        <v>-1.847090315706638</v>
+        <v>-1.970055577805019</v>
       </c>
       <c r="G89">
-        <v>0.9576767734775743</v>
+        <v>1.497964426577711</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.893086946089132</v>
       </c>
       <c r="E90">
-        <v>-21.33122039324855</v>
+        <v>-20.44834910071314</v>
       </c>
       <c r="F90">
-        <v>-1.69419380365941</v>
+        <v>-1.744183480880256</v>
       </c>
       <c r="G90">
-        <v>0.3612985473055664</v>
+        <v>1.583479128402625</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.039980545957592</v>
       </c>
       <c r="E91">
-        <v>-23.65951719039624</v>
+        <v>-23.17596673585719</v>
       </c>
       <c r="F91">
-        <v>-1.571411459594263</v>
+        <v>-1.593644315088159</v>
       </c>
       <c r="G91">
-        <v>1.047243583042556</v>
+        <v>0.963642376539341</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.205450021133506</v>
       </c>
       <c r="E92">
-        <v>-25.04826884280251</v>
+        <v>-24.32443755741648</v>
       </c>
       <c r="F92">
-        <v>-1.748142745668855</v>
+        <v>-1.632934475144297</v>
       </c>
       <c r="G92">
-        <v>0.8684410184665196</v>
+        <v>1.6209313300884</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.385609471216679</v>
       </c>
       <c r="E93">
-        <v>-27.17145293824677</v>
+        <v>-27.09245370918297</v>
       </c>
       <c r="F93">
-        <v>-1.987458922109783</v>
+        <v>-1.818015058805085</v>
       </c>
       <c r="G93">
-        <v>0.4795744077871081</v>
+        <v>1.204759339801079</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.573671586684905</v>
       </c>
       <c r="E94">
-        <v>-29.56116942836049</v>
+        <v>-29.50462463766371</v>
       </c>
       <c r="F94">
-        <v>-1.804666793496804</v>
+        <v>-1.845644392205842</v>
       </c>
       <c r="G94">
-        <v>-0.1246961589505224</v>
+        <v>0.9248328511824649</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.765566915194309</v>
       </c>
       <c r="E95">
-        <v>-31.59820383428283</v>
+        <v>-30.56310788797958</v>
       </c>
       <c r="F95">
-        <v>-1.744017191759135</v>
+        <v>-1.928302755050373</v>
       </c>
       <c r="G95">
-        <v>0.1409453256661369</v>
+        <v>1.057423510575815</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.953126841085278</v>
       </c>
       <c r="E96">
-        <v>-34.19165863423864</v>
+        <v>-33.40009722735689</v>
       </c>
       <c r="F96">
-        <v>-2.182259500826581</v>
+        <v>-2.163265323929758</v>
       </c>
       <c r="G96">
-        <v>0.3150601577585657</v>
+        <v>0.6399405442549436</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.131765007024944</v>
       </c>
       <c r="E97">
-        <v>-36.38936556219013</v>
+        <v>-35.34374317805605</v>
       </c>
       <c r="F97">
-        <v>-2.329387364076821</v>
+        <v>-1.872949065893933</v>
       </c>
       <c r="G97">
-        <v>-0.1530675342220765</v>
+        <v>0.2139428548070665</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.2932168588502</v>
       </c>
       <c r="E98">
-        <v>-39.13294833244823</v>
+        <v>-38.44869590988924</v>
       </c>
       <c r="F98">
-        <v>-2.120004021290657</v>
+        <v>-2.063915492589453</v>
       </c>
       <c r="G98">
-        <v>-0.7531171553971363</v>
+        <v>0.0405331689145025</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.43384583918642</v>
       </c>
       <c r="E99">
-        <v>-41.37949258833544</v>
+        <v>-41.21005294062744</v>
       </c>
       <c r="F99">
-        <v>-2.343534609019442</v>
+        <v>-2.031522371795055</v>
       </c>
       <c r="G99">
-        <v>-0.4174874275347448</v>
+        <v>-0.210730616425102</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.545191786733583</v>
       </c>
       <c r="E100">
-        <v>-44.07146886880213</v>
+        <v>-43.04699445828386</v>
       </c>
       <c r="F100">
-        <v>-2.649137588404046</v>
+        <v>-2.2016994909386</v>
       </c>
       <c r="G100">
-        <v>-1.225349923846475</v>
+        <v>-0.3432451332710491</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.622286807203495</v>
       </c>
       <c r="E101">
-        <v>-45.82154519804342</v>
+        <v>-46.17668850785796</v>
       </c>
       <c r="F101">
-        <v>-2.723901969113069</v>
+        <v>-2.338806455008897</v>
       </c>
       <c r="G101">
-        <v>-1.623184802391772</v>
+        <v>-0.7270168143655222</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.652155851166363</v>
       </c>
       <c r="E102">
-        <v>-48.14634374902018</v>
+        <v>-49.63302478396083</v>
       </c>
       <c r="F102">
-        <v>-2.672666707189729</v>
+        <v>-2.634623715542001</v>
       </c>
       <c r="G102">
-        <v>-1.78185925008904</v>
+        <v>-1.096963657287999</v>
       </c>
     </row>
   </sheetData>
